--- a/output/roomself_excel/4929.xlsx
+++ b/output/roomself_excel/4929.xlsx
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>175458</v>
+        <v>110510</v>
       </c>
       <c r="D2" t="n">
-        <v>3520</v>
+        <v>3028</v>
       </c>
       <c r="E2" t="n">
-        <v>494</v>
+        <v>459</v>
       </c>
       <c r="F2" t="n">
-        <v>461</v>
+        <v>347</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>164892</v>
+        <v>20412</v>
       </c>
       <c r="D3" t="n">
-        <v>3268</v>
+        <v>1152</v>
       </c>
       <c r="E3" t="n">
-        <v>498</v>
+        <v>126</v>
       </c>
       <c r="F3" t="n">
-        <v>392</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4">
@@ -514,16 +514,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>20412</v>
+        <v>50250</v>
       </c>
       <c r="D4" t="n">
-        <v>1152</v>
+        <v>2036</v>
       </c>
       <c r="E4" t="n">
-        <v>126</v>
+        <v>319</v>
       </c>
       <c r="F4" t="n">
-        <v>23</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5">
@@ -542,10 +542,10 @@
         <v>3292</v>
       </c>
       <c r="E5" t="n">
-        <v>595</v>
+        <v>436</v>
       </c>
       <c r="F5" t="n">
-        <v>498</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6">
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>49548</v>
+        <v>14637</v>
       </c>
       <c r="D6" t="n">
-        <v>2572</v>
+        <v>968</v>
       </c>
       <c r="E6" t="n">
-        <v>494</v>
+        <v>149</v>
       </c>
       <c r="F6" t="n">
-        <v>185</v>
+        <v>141</v>
       </c>
     </row>
     <row r="7">
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>50250</v>
+        <v>45743</v>
       </c>
       <c r="D7" t="n">
-        <v>2036</v>
+        <v>1824</v>
       </c>
       <c r="E7" t="n">
-        <v>528</v>
+        <v>307</v>
       </c>
       <c r="F7" t="n">
-        <v>494</v>
+        <v>173</v>
       </c>
     </row>
     <row r="8">
@@ -598,20 +598,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>110510</v>
+        <v>175458</v>
       </c>
       <c r="D8" t="n">
-        <v>3028</v>
+        <v>3520</v>
       </c>
       <c r="E8" t="n">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="F8" t="n">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="9">
@@ -624,16 +624,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>101105</v>
+        <v>164892</v>
       </c>
       <c r="D9" t="n">
-        <v>2568</v>
+        <v>3268</v>
       </c>
       <c r="E9" t="n">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="F9" t="n">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="10">
@@ -646,16 +646,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>24734</v>
+        <v>49548</v>
       </c>
       <c r="D10" t="n">
-        <v>1260</v>
+        <v>2572</v>
       </c>
       <c r="E10" t="n">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="F10" t="n">
-        <v>183</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11">
@@ -664,20 +664,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>14637</v>
+        <v>101105</v>
       </c>
       <c r="D11" t="n">
-        <v>968</v>
+        <v>2568</v>
       </c>
       <c r="E11" t="n">
-        <v>149</v>
+        <v>394</v>
       </c>
       <c r="F11" t="n">
-        <v>141</v>
+        <v>300</v>
       </c>
     </row>
     <row r="12">
@@ -686,20 +686,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>45743</v>
+        <v>24734</v>
       </c>
       <c r="D12" t="n">
-        <v>1824</v>
+        <v>1260</v>
       </c>
       <c r="E12" t="n">
-        <v>307</v>
+        <v>195</v>
       </c>
       <c r="F12" t="n">
-        <v>173</v>
+        <v>183</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/4929.xlsx
+++ b/output/roomself_excel/4929.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,47 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
         </is>
       </c>
     </row>
@@ -475,11 +510,38 @@
       <c r="D2" t="n">
         <v>3028</v>
       </c>
-      <c r="E2" t="n">
-        <v>459</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>347</v>
+        <v>61</v>
+      </c>
+      <c r="G2" t="n">
+        <v>57</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>372</v>
+      </c>
+      <c r="J2" t="n">
+        <v>23</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>167</v>
+      </c>
+      <c r="M2" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="3">
@@ -497,12 +559,23 @@
       <c r="D3" t="n">
         <v>1152</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
         <v>126</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>23</v>
       </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,12 +592,31 @@
       <c r="D4" t="n">
         <v>2036</v>
       </c>
-      <c r="E4" t="n">
-        <v>319</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F4" t="n">
+        <v>268</v>
+      </c>
+      <c r="G4" t="n">
+        <v>21</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>51</v>
+      </c>
+      <c r="J4" t="n">
         <v>49</v>
       </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,12 +633,23 @@
       <c r="D5" t="n">
         <v>3292</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
         <v>436</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>22</v>
       </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +666,31 @@
       <c r="D6" t="n">
         <v>968</v>
       </c>
-      <c r="E6" t="n">
-        <v>149</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F6" t="n">
-        <v>141</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="G6" t="n">
+        <v>22</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>119</v>
+      </c>
+      <c r="J6" t="n">
+        <v>26</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,11 +707,38 @@
       <c r="D7" t="n">
         <v>1824</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
         <v>307</v>
       </c>
-      <c r="F7" t="n">
-        <v>173</v>
+      <c r="G7" t="n">
+        <v>11</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>307</v>
+      </c>
+      <c r="J7" t="n">
+        <v>13</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>149</v>
+      </c>
+      <c r="M7" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="8">
@@ -607,11 +756,38 @@
       <c r="D8" t="n">
         <v>3520</v>
       </c>
-      <c r="E8" t="n">
-        <v>494</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F8" t="n">
-        <v>461</v>
+        <v>450</v>
+      </c>
+      <c r="G8" t="n">
+        <v>31</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>430</v>
+      </c>
+      <c r="J8" t="n">
+        <v>21</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>368</v>
+      </c>
+      <c r="M8" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="9">
@@ -629,11 +805,38 @@
       <c r="D9" t="n">
         <v>3268</v>
       </c>
-      <c r="E9" t="n">
-        <v>498</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F9" t="n">
-        <v>392</v>
+        <v>453</v>
+      </c>
+      <c r="G9" t="n">
+        <v>28</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>364</v>
+      </c>
+      <c r="J9" t="n">
+        <v>23</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>364</v>
+      </c>
+      <c r="M9" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="10">
@@ -651,12 +854,23 @@
       <c r="D10" t="n">
         <v>2572</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
         <v>185</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>23</v>
       </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +887,31 @@
       <c r="D11" t="n">
         <v>2568</v>
       </c>
-      <c r="E11" t="n">
-        <v>394</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F11" t="n">
-        <v>300</v>
-      </c>
+        <v>365</v>
+      </c>
+      <c r="G11" t="n">
+        <v>23</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>277</v>
+      </c>
+      <c r="J11" t="n">
+        <v>29</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,12 +928,31 @@
       <c r="D12" t="n">
         <v>1260</v>
       </c>
-      <c r="E12" t="n">
-        <v>195</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F12" t="n">
-        <v>183</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="G12" t="n">
+        <v>34</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>149</v>
+      </c>
+      <c r="J12" t="n">
+        <v>29</v>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/roomself_excel/4929.xlsx
+++ b/output/roomself_excel/4929.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rooms" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:Q12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -494,6 +494,26 @@
           <t>ExtWallWidth_3</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_1</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_1</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_1</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_1</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -541,6 +561,22 @@
         <v>167</v>
       </c>
       <c r="M2" t="n">
+        <v>26</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>153</v>
+      </c>
+      <c r="Q2" t="n">
         <v>26</v>
       </c>
     </row>
@@ -576,6 +612,10 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -617,6 +657,10 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -650,6 +694,10 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -691,6 +739,22 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>96</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -740,6 +804,22 @@
       <c r="M7" t="n">
         <v>13</v>
       </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>82</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -789,6 +869,22 @@
       <c r="M8" t="n">
         <v>23</v>
       </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>184</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>31</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -837,6 +933,22 @@
       </c>
       <c r="M9" t="n">
         <v>22</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>183</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="10">
@@ -871,6 +983,10 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -912,6 +1028,22 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>123</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>29</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -953,6 +1085,22 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>66</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>29</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
